--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>miczupl</v>
+        <v>superpapipig</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>superpapipig</v>
+        <v>rionnad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rionnad</v>
+        <v>maito1794</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>maito1794</v>
+        <v>snekiecr8</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>any_one_plz</v>
+        <v>clown_noes666</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>clown_noes666</v>
+        <v>flippy826</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_artist.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_artist.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>flippy826</v>
+        <v>uplift3ntree</v>
       </c>
     </row>
   </sheetData>
